--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/5608-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/5608-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA54E08F-834C-4F62-8806-554DD31B2DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8D548FA-E933-4E21-81E1-5A38506379CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E53F70D5-880E-4A8C-96CA-385D0D171ACA}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{462744FE-331A-4099-B25B-99D5F6AA6CB4}"/>
   </bookViews>
   <sheets>
     <sheet name="5608-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1403,24 +1403,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A14EC2EA-D67A-443B-88AD-2AC2845E5BB4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04B8B576-89CE-4F05-A089-ACC9F0FECDED}">
   <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" customWidth="1"/>
-    <col min="6" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" customWidth="1"/>
-    <col min="9" max="10" width="7.6640625" customWidth="1"/>
-    <col min="11" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="1" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="7" width="9.5" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="10" width="9.5" customWidth="1"/>
+    <col min="11" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1448,7 +1448,7 @@
       <c r="Q1" s="28"/>
       <c r="R1" s="20"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1478,7 +1478,7 @@
       <c r="Q2" s="30"/>
       <c r="R2" s="31"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1524,7 +1524,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1574,7 +1574,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="37">
         <v>2024</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="35">
         <v>2023</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>6.68</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="37">
         <v>2022</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>6.01</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="35">
         <v>2021</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2020</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="35">
         <v>2019</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>2018</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="35">
         <v>2017</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="37">
         <v>2016</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="35">
         <v>2015</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>6.96</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>2014</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="35">
         <v>2013</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2012</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="35">
         <v>2011</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2010</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>8.68</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="35">
         <v>2009</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>9.08</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2008</v>
       </c>
@@ -2546,7 +2546,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="35">
         <v>2007</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2006</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="35">
         <v>2005</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2004</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="35">
         <v>2003</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2002</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>5.04</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="35">
         <v>2001</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2000</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="35">
         <v>1999</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37" t="s">
         <v>25</v>
       </c>
